--- a/historico.xlsx
+++ b/historico.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,6 +834,46 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46035.48244212963</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Usuário César fez login</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>César</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46035.48644675926</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ATUALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Contrato 1052024 atualizado. Motivo: Teste. Alterações: Data Fim Prevista: 31/01/2026 → 26/02/2026 | Observações alteradas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
